--- a/public/as-made/files/AS-MADE_siemens-4-shutters.xlsx
+++ b/public/as-made/files/AS-MADE_siemens-4-shutters.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="רשימות" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'הוראות מילוי · تعليمات'!$A$1:$B$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'הוראות מילוי · تعليمات'!$A$1:$B$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'טופס AS-MADE'!$10:$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77,6 +77,10 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="009CA3AF"/>
       <sz val="10"/>
@@ -105,10 +109,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -176,16 +176,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,14 +220,14 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -235,8 +235,8 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -701,211 +701,197 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="15" customHeight="1">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>•  בבקרי תריסים: "זמן נסיעה מלא" — כמה שניות לוקח לתריס לרדת מפתוח לגמרי לסגור לגמרי. מדוד/י בפועל עם סטופר. בלי הזמן הזה אי אפשר לתכנת מיקום באחוזים.</t>
+          <t>•  "נבדק בשטח" — סמן/י "כן" רק אחרי שהפעלת את המעגל וראית שהוא עובד.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>•  "נבדק בשטח" — סמן/י "כן" רק אחרי שהפעלת את המעגל וראית שהוא עובד.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
           <t>•  ערוץ שאינו בשימוש — השאר/י ריק. אל תמחק/י את השורה.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="17" ht="21" customHeight="1">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>מה לא ממלאים</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="6" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>•  כל תא אפור שרשום בו "ימולא ע"י I FEEL" — נעול. הכתובת הפיזית, כתובות הקבוצה ושמות האובייקטים ב-ETS נקבעים אצלנו בשלב התכנות.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="5" t="inlineStr">
+    <row r="19" ht="21" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>שליחה</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>•  מלא/י באתר i-feel.co.il ולחץ/י "שליחה" — הטופס מגיע ישירות למנהל הפרויקט, או שמור/י את הקובץ ושלח/י אותו במייל.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>•  מלא/י באתר i-feel.co.il ולחץ/י "שליחה" — הטופס מגיע ישירות למנהל הפרויקט, או שמור/י את הקובץ ושלח/י אותו במייל.</t>
+          <t>•  מומלץ לצרף גם צילום של הלוח הפתוח ושל סימון הכבלים.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>•  מומלץ לצרף גם צילום של הלוח הפתוח ושל סימון הכבלים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
           <t>•  שאלות: I FEEL · 03-508-9553 · i-feel.co.il</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>كيفية تعبئة النموذج — تعليمات للكهربائي</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>هذا النموذج هو مخطط AS-MADE للوحة الكهرباء. بناءً عليه نقوم في I FEEL ببرمجة وحدات التحكم في ETS6. ما لا يُكتب هنا — لن تتم برمجته.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="5" t="inlineStr">
+    <row r="27" ht="21" customHeight="1">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>قبل البدء</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>•  تأكّد من أن اللوحة موصولة فعلياً وأن ترقيم الكابلات مطابق لما هو مكتوب في النموذج.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>•  تأكّد من أن اللوحة موصولة فعلياً وأن ترقيم الكابلات مطابق لما هو مكتوب في النموذج.</t>
+          <t>•  عبّئ تفاصيل المشروع في أعلى النموذج: اسم المشروع، عنوان الموقع، رقم اللوحة، اسمك، رقم هاتفك وبريدك الإلكتروني.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>•  عبّئ تفاصيل المشروع في أعلى النموذج: اسم المشروع، عنوان الموقع، رقم اللوحة، اسمك، رقم هاتفك وبريدك الإلكتروني.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
           <t>•  إذا كانت اللوحة تحتوي على عدة وحدات من النوع نفسه — النموذج مقسّم مسبقاً إلى كتل: وحدة P1، وحدة P2 وهكذا. الوحدة غير الموجودة — اترك كتلتها فارغة.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
+    <row r="31" ht="21" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>التعبئة سطراً سطراً</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>•  كل سطر = قناة واحدة في وحدة التحكم. ترتيب القنوات في النموذج مطابق لترتيب المشابك.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>•  كل سطر = قناة واحدة في وحدة التحكم. ترتيب القنوات في النموذج مطابق لترتيب المشابك.</t>
+          <t>•  "الغرفة / المنطقة" — اسم الغرفة كما يسميها الزبون: صالون، مطبخ، غرفة نوم، شرفة.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>•  "الغرفة / المنطقة" — اسم الغرفة كما يسميها الزبون: صالون، مطبخ، غرفة نوم، شرفة.</t>
+          <t>•  "وصف الدائرة / الحمل" — ما هو الموصول فعلياً: سبوتات المطبخ، ثريا غرفة الطعام، إنارة الحديقة.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>•  "وصف الدائرة / الحمل" — ما هو الموصول فعلياً: سبوتات المطبخ، ثريا غرفة الطعام، إنارة الحديقة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
+          <t>•  "نوع الحمل" و"الوظيفة المطلوبة" — اختر من القائمة المنسدلة فقط. لا تكتب نصاً حراً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>•  "نوع الحمل" و"الوظيفة المطلوبة" — اختر من القائمة المنسدلة فقط. لا تكتب نصاً حراً.</t>
+          <t>•  "القدرة / الكمية" — تيار القاطع (مثلاً 10A) أو القدرة بالواط.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>•  "القدرة / الكمية" — تيار القاطع (مثلاً 10A) أو القدرة بالواط.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="41" customHeight="1">
+          <t>•  "تم الفحص في الموقع" — ضع "نعم" فقط بعد تشغيل الدائرة والتأكد من عملها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>•  في وحدات الستائر: "زمن الحركة الكامل" — كم ثانية تحتاج الستارة للنزول من الفتح الكامل حتى الإغلاق الكامل. قِس بساعة إيقاف. بدون هذا الزمن لا يمكن برمجة الموضع بالنسبة المئوية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>•  "تم الفحص في الموقع" — ضع "نعم" فقط بعد تشغيل الدائرة والتأكد من عملها.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
+          <t>•  القناة غير المستخدمة — اتركها فارغة. لا تحذف السطر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>ما لا يجب تعبئته</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>•  القناة غير المستخدمة — اتركها فارغة. لا تحذف السطر.</t>
+          <t>•  كل خانة رمادية مكتوب فيها "ימולא ע"י I FEEL" — مقفلة. العنوان الفيزيائي وعناوين المجموعات وأسماء الكائنات في ETS تُحدَّد لدينا في مرحلة البرمجة.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>ما لا يجب تعبئته</t>
+          <t>الإرسال</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>•  كل خانة رمادية مكتوب فيها "ימולא ע"י I FEEL" — مقفلة. العنوان الفيزيائي وعناوين المجموعات وأسماء الكائنات في ETS تُحدَّد لدينا في مرحلة البرمجة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="21" customHeight="1">
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>الإرسال</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
+          <t>•  عبّئ النموذج في موقع i-feel.co.il واضغط "إرسال" — يصل مباشرة إلى مدير المشروع، أو احفظ الملف وأرسله بالبريد الإلكتروني.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>•  يُفضّل إرفاق صورة للوحة مفتوحة ولترقيم الكابلات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
       <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>•  عبّئ النموذج في موقع i-feel.co.il واضغط "إرسال" — يصل مباشرة إلى مدير المشروع، أو احفظ الملف وأرسله بالبريد الإلكتروني.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>•  يُفضّل إرفاق صورة للوحة مفتوحة ولترقيم الكابلات.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>•  للاستفسار: I FEEL · 03-508-9553 · i-feel.co.il</t>
         </is>
@@ -927,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -937,14 +923,13 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -966,7 +951,6 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -1122,40 +1106,35 @@
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <t>זמן נסיעה מלא (שנ')</t>
+          <t>למלים / הצללה</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>למלים / הצללה</t>
+          <t>פעולה רצויה</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>פעולה רצויה</t>
+          <t>כתובת קבוצה - פקודה</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>כתובת קבוצה - פקודה</t>
+          <t>כתובת קבוצה - מיקום</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>כתובת קבוצה - מיקום</t>
+          <t>שם אובייקט ב-ETS</t>
         </is>
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>שם אובייקט ב-ETS</t>
+          <t>נבדק בשטח</t>
         </is>
       </c>
       <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>נבדק בשטח</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
         <is>
           <t>הערות</t>
         </is>
@@ -1199,40 +1178,35 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>زمن الحركة الكامل (ث)</t>
+          <t>الشرائح / التظليل</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>الشرائح / التظليل</t>
+          <t>الوظيفة المطلوبة</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>الوظيفة المطلوبة</t>
+          <t>عنوان المجموعة - الأمر</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>عنوان المجموعة - الأمر</t>
+          <t>عنوان المجموعة - الموضع</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>عنوان المجموعة - الموضع</t>
+          <t>اسم الكائن في ETS</t>
         </is>
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>اسم الكائن في ETS</t>
+          <t>تم الفحص في الموقع</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>تم الفحص في الموقع</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
@@ -1274,40 +1248,35 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>כן</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
+          <t>עלייה / ירידה / עצירה + הצללה</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="inlineStr">
+        <is>
           <t>כן</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>עלייה / ירידה / עצירה + הצללה</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
       <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="O12" s="18" t="inlineStr">
         <is>
           <t>שורת דוגמה – نموذج – נא למחוק</t>
         </is>
@@ -1337,7 +1306,11 @@
       <c r="G13" s="20" t="n"/>
       <c r="H13" s="20" t="n"/>
       <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1348,13 +1321,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M13" s="20" t="n"/>
       <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -1380,7 +1348,11 @@
       <c r="G14" s="20" t="n"/>
       <c r="H14" s="20" t="n"/>
       <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K14" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1391,13 +1363,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M14" s="20" t="n"/>
       <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
@@ -1423,7 +1390,11 @@
       <c r="G15" s="20" t="n"/>
       <c r="H15" s="20" t="n"/>
       <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K15" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1434,13 +1405,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M15" s="20" t="n"/>
       <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -1466,7 +1432,11 @@
       <c r="G17" s="20" t="n"/>
       <c r="H17" s="20" t="n"/>
       <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K17" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1477,13 +1447,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M17" s="20" t="n"/>
       <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -1509,7 +1474,11 @@
       <c r="G18" s="20" t="n"/>
       <c r="H18" s="20" t="n"/>
       <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K18" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1520,13 +1489,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M18" s="20" t="n"/>
       <c r="N18" s="11" t="n"/>
-      <c r="O18" s="11" t="n"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
@@ -1552,7 +1516,11 @@
       <c r="G19" s="20" t="n"/>
       <c r="H19" s="20" t="n"/>
       <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K19" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1563,13 +1531,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M19" s="20" t="n"/>
       <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -1595,7 +1558,11 @@
       <c r="G20" s="20" t="n"/>
       <c r="H20" s="20" t="n"/>
       <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K20" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1606,13 +1573,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M20" s="20" t="n"/>
       <c r="N20" s="11" t="n"/>
-      <c r="O20" s="11" t="n"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
@@ -1638,7 +1600,11 @@
       <c r="G22" s="20" t="n"/>
       <c r="H22" s="20" t="n"/>
       <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K22" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1649,13 +1615,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M22" s="20" t="n"/>
       <c r="N22" s="11" t="n"/>
-      <c r="O22" s="11" t="n"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
@@ -1681,7 +1642,11 @@
       <c r="G23" s="20" t="n"/>
       <c r="H23" s="20" t="n"/>
       <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K23" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1692,13 +1657,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M23" s="20" t="n"/>
       <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
@@ -1724,7 +1684,11 @@
       <c r="G24" s="20" t="n"/>
       <c r="H24" s="20" t="n"/>
       <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K24" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1735,13 +1699,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M24" s="20" t="n"/>
       <c r="N24" s="11" t="n"/>
-      <c r="O24" s="11" t="n"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -1767,7 +1726,11 @@
       <c r="G25" s="20" t="n"/>
       <c r="H25" s="20" t="n"/>
       <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K25" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1778,13 +1741,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M25" s="20" t="n"/>
       <c r="N25" s="11" t="n"/>
-      <c r="O25" s="11" t="n"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
@@ -1810,7 +1768,11 @@
       <c r="G27" s="20" t="n"/>
       <c r="H27" s="20" t="n"/>
       <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K27" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1821,13 +1783,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M27" s="20" t="n"/>
       <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -1853,7 +1810,11 @@
       <c r="G28" s="20" t="n"/>
       <c r="H28" s="20" t="n"/>
       <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K28" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1864,13 +1825,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M28" s="20" t="n"/>
       <c r="N28" s="11" t="n"/>
-      <c r="O28" s="11" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -1896,7 +1852,11 @@
       <c r="G29" s="20" t="n"/>
       <c r="H29" s="20" t="n"/>
       <c r="I29" s="20" t="n"/>
-      <c r="J29" s="20" t="n"/>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K29" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1907,13 +1867,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M29" s="20" t="n"/>
       <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="n"/>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -1939,7 +1894,11 @@
       <c r="G30" s="20" t="n"/>
       <c r="H30" s="20" t="n"/>
       <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>ימולא ע"י I FEEL</t>
+        </is>
+      </c>
       <c r="K30" s="16" t="inlineStr">
         <is>
           <t>ימולא ע"י I FEEL</t>
@@ -1950,13 +1909,8 @@
           <t>ימולא ע"י I FEEL</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr">
-        <is>
-          <t>ימולא ע"י I FEEL</t>
-        </is>
-      </c>
+      <c r="M30" s="20" t="n"/>
       <c r="N30" s="11" t="n"/>
-      <c r="O30" s="11" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1" password="C7FC"/>
@@ -1965,19 +1919,19 @@
     <mergeCell ref="K7:N7"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="K6:N6"/>
-    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="K5:N5"/>
     <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A2:N2"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A1:O1"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="H6:J6"/>
@@ -1986,13 +1940,13 @@
     <dataValidation sqref="G12:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
       <formula1>=רשימות!$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="I12:I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
+    <dataValidation sqref="H12:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
       <formula1>=רשימות!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="J12:J30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
+    <dataValidation sqref="I12:I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
       <formula1>=רשימות!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation sqref="N12:N30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
+    <dataValidation sqref="M12:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא חוקי" error="יש לבחור ערך מהרשימה  ·  الرجاء اختيار قيمة من القائمة" type="list">
       <formula1>=רשימות!$D$2:$D$4</formula1>
     </dataValidation>
   </dataValidations>
